--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486871_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486871_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. CASADO FAJO</t>
+          <t>P. ASO JIMENEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,58 +565,58 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>0.3538</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>-0.0587</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>0.4125</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1395</v>
+        <v>-0.9247</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1395</v>
+        <v>-0.6391</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>-0.2096</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>-0.2886</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>0.0789</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1395</v>
+        <v>-0.7151</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1395</v>
+        <v>-0.7181</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>0.8214</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>0.8214</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1395</v>
+        <v>0.4571</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>0.151</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1395</v>
+        <v>0.3062</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. ASO JIMENEZ</t>
+          <t>M. CASADO FAJO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,58 +643,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0538</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.2292</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1754</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.9247</v>
+        <v>0.1395</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6391</v>
+        <v>0.1395</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.2096</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.2886</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0789</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7151</v>
+        <v>0.1395</v>
       </c>
       <c r="N3" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.7181</v>
+        <v>0.1395</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8214</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8214</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0495</v>
+        <v>-0.1395</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0195</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.06900000000000001</v>
+        <v>-0.1395</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. ARJOL LOPEZ</t>
+          <t>O. ALVARADO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.9577</v>
+        <v>-0.6569</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1934</v>
+        <v>0.4157</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7643</v>
+        <v>-1.0726</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.3385</v>
+        <v>-0.7763</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1912</v>
+        <v>0.0291</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.1472</v>
+        <v>-0.8054</v>
       </c>
       <c r="J4" t="n">
-        <v>1.0389</v>
+        <v>2.1826</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4473</v>
+        <v>0.5518999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.4084</v>
+        <v>1.6308</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.3773</v>
+        <v>-2.9589</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.6385</v>
+        <v>-0.5228</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.7388</v>
+        <v>-2.4362</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>1.0267</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.0534</v>
+        <v>-1.2321</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0534</v>
+        <v>2.2588</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0381</v>
+        <v>-1.0161</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1004</v>
+        <v>-0.5349</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1386</v>
+        <v>-0.4812</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4189</v>
+        <v>0.1088</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7207</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6982</v>
+        <v>0.1088</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>O. ALVARADO RODRIGUEZ</t>
+          <t>D. ARJOL LOPEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.4459</v>
+        <v>-1.0147</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3437</v>
+        <v>-0.3096</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.1022</v>
+        <v>-0.7050999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.7763</v>
+        <v>-2.3385</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0291</v>
+        <v>-0.1912</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8054</v>
+        <v>-2.1472</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1826</v>
+        <v>1.0389</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5518999999999999</v>
+        <v>1.4473</v>
       </c>
       <c r="L5" t="n">
-        <v>1.6308</v>
+        <v>-0.4084</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.9589</v>
+        <v>-3.3773</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5228</v>
+        <v>-1.6385</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.4362</v>
+        <v>-1.7388</v>
       </c>
       <c r="P5" t="n">
-        <v>1.0267</v>
+        <v>-0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.2321</v>
+        <v>-2.0534</v>
       </c>
       <c r="R5" t="n">
-        <v>2.2588</v>
+        <v>2.0534</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.8051</v>
+        <v>-0.095</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.2943</v>
+        <v>-0.0157</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5109</v>
+        <v>-0.0793</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1088</v>
+        <v>1.4189</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.7207</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1088</v>
+        <v>0.6982</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.7407</v>
+        <v>-2.346</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.1814</v>
+        <v>-2.6385</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4407</v>
+        <v>0.2925</v>
       </c>
       <c r="G6" t="n">
         <v>-0.9949</v>
@@ -922,13 +922,13 @@
         <v>1.0267</v>
       </c>
       <c r="S6" t="n">
-        <v>0.246</v>
+        <v>-0.3593</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5461</v>
+        <v>0.089</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3001</v>
+        <v>-0.4483</v>
       </c>
       <c r="V6" t="n">
         <v>0.2402</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.1296</v>
+        <v>-2.5083</v>
       </c>
       <c r="E7" t="n">
-        <v>2.0338</v>
+        <v>2.0997</v>
       </c>
       <c r="F7" t="n">
-        <v>-4.1634</v>
+        <v>-4.608</v>
       </c>
       <c r="G7" t="n">
         <v>-2.274</v>
@@ -1000,13 +1000,13 @@
         <v>1.6427</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4668</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3257</v>
+        <v>-0.2598</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7925</v>
+        <v>0.3479</v>
       </c>
       <c r="V7" t="n">
         <v>-0.9384</v>
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.2052</v>
+        <v>-2.767</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1869</v>
+        <v>-0.7486</v>
       </c>
       <c r="F8" t="n">
         <v>-2.0184</v>
@@ -1078,10 +1078,10 @@
         <v>2.0534</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.159</v>
+        <v>-0.7207</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6274</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="U8" t="n">
         <v>-0.7864</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.6462</v>
+        <v>-3.2648</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.6313</v>
+        <v>-2.0425</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0149</v>
+        <v>-1.2224</v>
       </c>
       <c r="G9" t="n">
         <v>-4.058</v>
@@ -1156,13 +1156,13 @@
         <v>0.616</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2042</v>
+        <v>0.1772</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.775</v>
+        <v>-0.1861</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5708</v>
+        <v>0.3633</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.8252</v>
+        <v>-3.5313</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1111</v>
+        <v>-1.084</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.7141</v>
+        <v>-2.4473</v>
       </c>
       <c r="G10" t="n">
         <v>-3.0452</v>
@@ -1234,13 +1234,13 @@
         <v>2.0534</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.6897</v>
+        <v>-1.3958</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5387999999999999</v>
+        <v>-0.5116000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.151</v>
+        <v>-0.8842</v>
       </c>
       <c r="V10" t="n">
         <v>-0.9384</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.0658</v>
+        <v>-3.7471</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.4436</v>
+        <v>-3.2731</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6222</v>
+        <v>-0.474</v>
       </c>
       <c r="G11" t="n">
         <v>-6.3237</v>
@@ -1312,13 +1312,13 @@
         <v>2.0534</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3581</v>
+        <v>-1.0394</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5969</v>
+        <v>-0.4264</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7612</v>
+        <v>-0.613</v>
       </c>
       <c r="V11" t="n">
         <v>1.7679</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.8921</v>
+        <v>-5.4918</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.683</v>
+        <v>-3.342</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.2091</v>
+        <v>-2.1498</v>
       </c>
       <c r="G12" t="n">
         <v>-6.7524</v>
@@ -1390,13 +1390,13 @@
         <v>1.8481</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1931</v>
+        <v>0.2072</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7287</v>
+        <v>-0.3877</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5356</v>
+        <v>0.5949</v>
       </c>
       <c r="V12" t="n">
         <v>-0.5893</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-25.9622</v>
+        <v>-24.9741</v>
       </c>
       <c r="E13" t="n">
-        <v>-11.9698</v>
+        <v>-10.9816</v>
       </c>
       <c r="F13" t="n">
-        <v>-13.9925</v>
+        <v>-13.9926</v>
       </c>
       <c r="G13" t="n">
         <v>-29.6799</v>
@@ -1468,13 +1468,13 @@
         <v>16.4273</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.8245</v>
+        <v>-3.8363</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.005</v>
+        <v>-2.0165</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.8198</v>
+        <v>-1.8196</v>
       </c>
       <c r="V13" t="n">
         <v>-0.6981999999999998</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.6934</v>
+        <v>5.7571</v>
       </c>
       <c r="E14" t="n">
-        <v>3.1755</v>
+        <v>2.8617</v>
       </c>
       <c r="F14" t="n">
-        <v>3.5179</v>
+        <v>2.8954</v>
       </c>
       <c r="G14" t="n">
         <v>4.9192</v>
@@ -1546,13 +1546,13 @@
         <v>0.8214</v>
       </c>
       <c r="S14" t="n">
-        <v>1.9796</v>
+        <v>1.0433</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3098</v>
+        <v>-0.004</v>
       </c>
       <c r="U14" t="n">
-        <v>1.6697</v>
+        <v>1.0472</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. ABDULSALAM</t>
+          <t>C. HENDERSON</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.1978</v>
+        <v>5.2679</v>
       </c>
       <c r="E15" t="n">
-        <v>3.3314</v>
+        <v>5.8217</v>
       </c>
       <c r="F15" t="n">
-        <v>2.8664</v>
+        <v>-0.5538</v>
       </c>
       <c r="G15" t="n">
-        <v>3.9192</v>
+        <v>9.5854</v>
       </c>
       <c r="H15" t="n">
-        <v>3.1954</v>
+        <v>1.6317</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7238</v>
+        <v>7.9537</v>
       </c>
       <c r="J15" t="n">
-        <v>2.8081</v>
+        <v>8.3058</v>
       </c>
       <c r="K15" t="n">
-        <v>2.6897</v>
+        <v>1.0969</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1184</v>
+        <v>7.2088</v>
       </c>
       <c r="M15" t="n">
-        <v>1.1111</v>
+        <v>1.2796</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5057</v>
+        <v>0.5348000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6054</v>
+        <v>0.7449</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.8748</v>
+        <v>-1.4374</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.2855</v>
+        <v>-2.0534</v>
       </c>
       <c r="R15" t="n">
-        <v>0.4107</v>
+        <v>0.616</v>
       </c>
       <c r="S15" t="n">
-        <v>4.0837</v>
+        <v>0.4156</v>
       </c>
       <c r="T15" t="n">
-        <v>2.739</v>
+        <v>-0.0815</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3447</v>
+        <v>0.4971</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0698</v>
+        <v>-3.2957</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0698</v>
+        <v>-0.3491</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-2.9466</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. HENDERSON</t>
+          <t>M. ABDULSALAM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.5068</v>
+        <v>4.5241</v>
       </c>
       <c r="E16" t="n">
-        <v>6.4493</v>
+        <v>1.9716</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.9426</v>
+        <v>2.5525</v>
       </c>
       <c r="G16" t="n">
-        <v>9.5854</v>
+        <v>3.9192</v>
       </c>
       <c r="H16" t="n">
-        <v>1.6317</v>
+        <v>3.1954</v>
       </c>
       <c r="I16" t="n">
-        <v>7.9537</v>
+        <v>0.7238</v>
       </c>
       <c r="J16" t="n">
-        <v>8.3058</v>
+        <v>2.8081</v>
       </c>
       <c r="K16" t="n">
-        <v>1.0969</v>
+        <v>2.6897</v>
       </c>
       <c r="L16" t="n">
-        <v>7.2088</v>
+        <v>0.1184</v>
       </c>
       <c r="M16" t="n">
-        <v>1.2796</v>
+        <v>1.1111</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5348000000000001</v>
+        <v>0.5057</v>
       </c>
       <c r="O16" t="n">
-        <v>0.7449</v>
+        <v>0.6054</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.4374</v>
+        <v>-2.8748</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.0534</v>
+        <v>-3.2855</v>
       </c>
       <c r="R16" t="n">
-        <v>0.616</v>
+        <v>0.4107</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6544</v>
+        <v>2.4099</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5461</v>
+        <v>1.3792</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1083</v>
+        <v>1.0308</v>
       </c>
       <c r="V16" t="n">
-        <v>-3.2957</v>
+        <v>1.0698</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.3491</v>
+        <v>1.0698</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.9466</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.2253</v>
+        <v>3.1197</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1439</v>
+        <v>0.0654</v>
       </c>
       <c r="F17" t="n">
-        <v>2.3691</v>
+        <v>3.0543</v>
       </c>
       <c r="G17" t="n">
         <v>0.4034</v>
@@ -1780,13 +1780,13 @@
         <v>0.8214</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7048</v>
+        <v>1.5992</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5229</v>
+        <v>0.7321</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1819</v>
+        <v>0.8671</v>
       </c>
       <c r="V17" t="n">
         <v>1.5277</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.1232</v>
+        <v>3.0925</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3139</v>
+        <v>-0.0001</v>
       </c>
       <c r="F18" t="n">
-        <v>2.4371</v>
+        <v>3.0926</v>
       </c>
       <c r="G18" t="n">
         <v>3.7166</v>
@@ -1858,13 +1858,13 @@
         <v>0.8214</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.039</v>
+        <v>-0.0696</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8486</v>
+        <v>-0.5348000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1904</v>
+        <v>0.4652</v>
       </c>
       <c r="V18" t="n">
         <v>-0.3491</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.6151</v>
+        <v>2.5216</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6345</v>
+        <v>2.2621</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0194</v>
+        <v>0.2595</v>
       </c>
       <c r="G19" t="n">
         <v>1.2043</v>
@@ -1936,13 +1936,13 @@
         <v>0.616</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2403</v>
+        <v>1.1469</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0504</v>
+        <v>0.5772</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2907</v>
+        <v>0.5697</v>
       </c>
       <c r="V19" t="n">
         <v>-0.2402</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. NVE MALEVA</t>
+          <t>A. MONTERO ISLA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.3553</v>
+        <v>1.9342</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1381</v>
+        <v>0.23</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4935</v>
+        <v>1.7042</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2609</v>
+        <v>2.9223</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2077</v>
+        <v>2.0985</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4686</v>
+        <v>0.8238</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1943</v>
+        <v>1.845</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7134</v>
+        <v>1.6741</v>
       </c>
       <c r="L20" t="n">
-        <v>0.9077</v>
+        <v>0.1709</v>
       </c>
       <c r="M20" t="n">
-        <v>0.06660000000000001</v>
+        <v>1.0773</v>
       </c>
       <c r="N20" t="n">
-        <v>0.5057</v>
+        <v>0.4244</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4391</v>
+        <v>0.6529</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.616</v>
+        <v>-2.8748</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0267</v>
+        <v>-3.2855</v>
       </c>
       <c r="R20" t="n">
         <v>0.4107</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2916</v>
+        <v>0.9483</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7246</v>
+        <v>0.4919</v>
       </c>
       <c r="U20" t="n">
-        <v>1.0162</v>
+        <v>0.4564</v>
       </c>
       <c r="V20" t="n">
-        <v>1.4189</v>
+        <v>0.9384</v>
       </c>
       <c r="W20" t="n">
-        <v>1.4189</v>
+        <v>1.1786</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5822000000000001</v>
+        <v>1.1227</v>
       </c>
       <c r="E21" t="n">
-        <v>1.3161</v>
+        <v>1.4207</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.734</v>
+        <v>-0.2981</v>
       </c>
       <c r="G21" t="n">
         <v>1.0936</v>
@@ -2092,13 +2092,13 @@
         <v>0.4107</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6819</v>
+        <v>-0.1414</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3216</v>
+        <v>-0.217</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3603</v>
+        <v>0.0756</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2402</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. MONTERO ISLA</t>
+          <t>J. NVE MALEVA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5377</v>
+        <v>1.0484</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.5022</v>
+        <v>-0.0335</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0399</v>
+        <v>1.0819</v>
       </c>
       <c r="G22" t="n">
-        <v>2.9223</v>
+        <v>0.2609</v>
       </c>
       <c r="H22" t="n">
-        <v>2.0985</v>
+        <v>-0.2077</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8238</v>
+        <v>0.4686</v>
       </c>
       <c r="J22" t="n">
-        <v>1.845</v>
+        <v>0.1943</v>
       </c>
       <c r="K22" t="n">
-        <v>1.6741</v>
+        <v>-0.7134</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1709</v>
+        <v>0.9077</v>
       </c>
       <c r="M22" t="n">
-        <v>1.0773</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>0.4244</v>
+        <v>0.5057</v>
       </c>
       <c r="O22" t="n">
-        <v>0.6529</v>
+        <v>-0.4391</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.8748</v>
+        <v>-0.616</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.2855</v>
+        <v>-1.0267</v>
       </c>
       <c r="R22" t="n">
         <v>0.4107</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4482</v>
+        <v>-0.0154</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2403</v>
+        <v>-0.62</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2079</v>
+        <v>0.6046</v>
       </c>
       <c r="V22" t="n">
-        <v>0.9384</v>
+        <v>1.4189</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1786</v>
+        <v>1.4189</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. AKINWOLE</t>
+          <t>E. ORTIZ TORRES</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1841</v>
+        <v>0.9822</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1579</v>
+        <v>-0.051</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0262</v>
+        <v>1.0332</v>
       </c>
       <c r="G23" t="n">
-        <v>0.7756999999999999</v>
+        <v>1.0574</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8627</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.08699999999999999</v>
+        <v>0.9762999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>1.146</v>
+        <v>0.1148</v>
       </c>
       <c r="K23" t="n">
-        <v>0.6069</v>
+        <v>-0.6745</v>
       </c>
       <c r="L23" t="n">
-        <v>0.5391</v>
+        <v>0.7893</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.3702</v>
+        <v>0.9425</v>
       </c>
       <c r="N23" t="n">
-        <v>0.2559</v>
+        <v>0.7554999999999999</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6261</v>
+        <v>0.187</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.616</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.2321</v>
+        <v>-1.0267</v>
       </c>
       <c r="R23" t="n">
-        <v>0.616</v>
+        <v>0.8214</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2646</v>
+        <v>0.0213</v>
       </c>
       <c r="T23" t="n">
-        <v>0.244</v>
+        <v>-0.3178</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0207</v>
+        <v>0.3391</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.2402</v>
+        <v>0.1088</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.2402</v>
+        <v>-1.0698</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>E. ORTIZ TORRES</t>
+          <t>A. AKINWOLE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0791</v>
+        <v>0.7612</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.2602</v>
+        <v>0.3671</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3393</v>
+        <v>0.3941</v>
       </c>
       <c r="G24" t="n">
-        <v>1.0574</v>
+        <v>0.7756999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.8627</v>
       </c>
       <c r="I24" t="n">
-        <v>0.9762999999999999</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>0.1148</v>
+        <v>1.146</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.6745</v>
+        <v>0.6069</v>
       </c>
       <c r="L24" t="n">
-        <v>0.7893</v>
+        <v>0.5391</v>
       </c>
       <c r="M24" t="n">
-        <v>0.9425</v>
+        <v>-0.3702</v>
       </c>
       <c r="N24" t="n">
-        <v>0.7554999999999999</v>
+        <v>0.2559</v>
       </c>
       <c r="O24" t="n">
-        <v>0.187</v>
+        <v>-0.6261</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.2053</v>
+        <v>-0.616</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.0267</v>
+        <v>-1.2321</v>
       </c>
       <c r="R24" t="n">
-        <v>0.8214</v>
+        <v>0.616</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8818</v>
+        <v>0.8417</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.527</v>
+        <v>0.4532</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3548</v>
+        <v>0.3885</v>
       </c>
       <c r="V24" t="n">
-        <v>0.1088</v>
+        <v>-0.2402</v>
       </c>
       <c r="W24" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.0698</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.1378</v>
+        <v>-0.6827</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.714</v>
+        <v>-0.9232</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.4238</v>
+        <v>0.2405</v>
       </c>
       <c r="G25" t="n">
         <v>-0.1781</v>
@@ -2404,13 +2404,13 @@
         <v>0.4107</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3437</v>
+        <v>0.1114</v>
       </c>
       <c r="T25" t="n">
-        <v>0.1704</v>
+        <v>-0.0388</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.514</v>
+        <v>0.1502</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>25.96220000000001</v>
+        <v>29.4489</v>
       </c>
       <c r="E26" t="n">
-        <v>13.9924</v>
+        <v>13.9925</v>
       </c>
       <c r="F26" t="n">
-        <v>11.9696</v>
+        <v>15.4563</v>
       </c>
       <c r="G26" t="n">
         <v>29.6799</v>
@@ -2458,7 +2458,7 @@
         <v>22.6846</v>
       </c>
       <c r="K26" t="n">
-        <v>7.6108</v>
+        <v>7.610799999999998</v>
       </c>
       <c r="L26" t="n">
         <v>15.0738</v>
@@ -2470,7 +2470,7 @@
         <v>6.045199999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>0.9501999999999998</v>
+        <v>0.9501999999999996</v>
       </c>
       <c r="P26" t="n">
         <v>-9.2402</v>
@@ -2482,13 +2482,13 @@
         <v>7.1871</v>
       </c>
       <c r="S26" t="n">
-        <v>4.824399999999999</v>
+        <v>8.311199999999999</v>
       </c>
       <c r="T26" t="n">
         <v>1.8197</v>
       </c>
       <c r="U26" t="n">
-        <v>3.0048</v>
+        <v>6.491499999999999</v>
       </c>
       <c r="V26" t="n">
         <v>0.6982000000000002</v>
